--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WYOMING_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WYOMING_2013.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C51">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C107">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C219">
